--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8929,0.0405,0.0291,0.0213</t>
-  </si>
-  <si>
-    <t>0.0289,0.0019,0.0008,0.9921</t>
-  </si>
-  <si>
-    <t>0.8198,0.0067,0.0010,0.2157</t>
-  </si>
-  <si>
-    <t>0.1349,0.0051,0.0022,0.9634</t>
-  </si>
-  <si>
-    <t>0.9898,0.0016,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9943,0.0006,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9865,0.0084,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9979,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9730,0.0541,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0015,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9949,0.0005,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9961,0.0005,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.2781,0.0374,0.7022,0.0620</t>
-  </si>
-  <si>
-    <t>0.4143,0.0047,0.6494,0.0164</t>
-  </si>
-  <si>
-    <t>0.4444,0.0725,0.6553,0.0033</t>
-  </si>
-  <si>
-    <t>0.1649,0.0475,0.8062,0.0052</t>
-  </si>
-  <si>
-    <t>0.7168,0.0083,0.3912,0.0041</t>
-  </si>
-  <si>
-    <t>0.0015,0.9930,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.0217,0.9668,0.0121,0.0006</t>
-  </si>
-  <si>
-    <t>0.0868,0.8944,0.0369,0.0009</t>
-  </si>
-  <si>
-    <t>0.0100,0.9804,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.9945,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.7323,0.0065,0.2900,0.0117</t>
-  </si>
-  <si>
-    <t>0.4444,0.0346,0.1957,0.4104</t>
-  </si>
-  <si>
-    <t>0.2044,0.0042,0.6018,0.1003</t>
-  </si>
-  <si>
-    <t>0.0477,0.0376,0.9024,0.0123</t>
-  </si>
-  <si>
-    <t>0.0214,0.0037,0.9762,0.0041</t>
-  </si>
-  <si>
-    <t>0.5345,0.0175,0.5400,0.0146</t>
-  </si>
-  <si>
-    <t>0.0197,0.0026,0.9769,0.0067</t>
-  </si>
-  <si>
-    <t>0.8376,0.2023,0.0212,0.0025</t>
-  </si>
-  <si>
-    <t>0.7093,0.1008,0.2567,0.0236</t>
-  </si>
-  <si>
-    <t>0.0024,0.0124,0.9854,0.0091</t>
-  </si>
-  <si>
-    <t>0.1013,0.7177,0.2769,0.0043</t>
-  </si>
-  <si>
-    <t>0.8921,0.0245,0.0288,0.0359</t>
-  </si>
-  <si>
-    <t>0.8395,0.0811,0.0687,0.0361</t>
-  </si>
-  <si>
-    <t>0.8096,0.3463,0.0045,0.0007</t>
-  </si>
-  <si>
-    <t>0.0138,0.9465,0.2494,0.0006</t>
-  </si>
-  <si>
-    <t>0.0152,0.8923,0.4164,0.0082</t>
-  </si>
-  <si>
-    <t>0.0739,0.0330,0.8446,0.0599</t>
-  </si>
-  <si>
-    <t>0.1473,0.1333,0.8171,0.0202</t>
-  </si>
-  <si>
-    <t>0.0339,0.0002,0.3066,0.5296</t>
-  </si>
-  <si>
-    <t>0.0178,0.4150,0.8663,0.0058</t>
-  </si>
-  <si>
-    <t>0.0031,0.9932,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0225,0.0537,0.9407,0.0050</t>
-  </si>
-  <si>
-    <t>0.2107,0.3267,0.0299,0.5999</t>
-  </si>
-  <si>
-    <t>0.0203,0.9382,0.0714,0.0142</t>
-  </si>
-  <si>
-    <t>0.0158,0.9483,0.1210,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.9810,0.3086,0.0007</t>
-  </si>
-  <si>
-    <t>0.0104,0.3408,0.9405,0.0060</t>
-  </si>
-  <si>
-    <t>0.0008,0.2145,0.9811,0.0021</t>
-  </si>
-  <si>
-    <t>0.3536,0.0198,0.6720,0.0351</t>
-  </si>
-  <si>
-    <t>0.0962,0.0063,0.9435,0.0018</t>
-  </si>
-  <si>
-    <t>0.0015,0.0068,0.9873,0.0140</t>
-  </si>
-  <si>
-    <t>0.0127,0.0145,0.9777,0.0026</t>
-  </si>
-  <si>
-    <t>0.9900,0.0022,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.9482,0.0271,0.0312,0.0018</t>
-  </si>
-  <si>
-    <t>0.9711,0.0245,0.0022,0.0015</t>
-  </si>
-  <si>
-    <t>0.0030,0.0499,0.9901,0.0006</t>
-  </si>
-  <si>
-    <t>0.9842,0.0038,0.0027,0.0022</t>
-  </si>
-  <si>
-    <t>0.9801,0.0093,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.9627,0.0242,0.0020,0.0042</t>
-  </si>
-  <si>
-    <t>0.0037,0.8867,0.7051,0.0010</t>
-  </si>
-  <si>
-    <t>0.0036,0.0076,0.9927,0.0009</t>
-  </si>
-  <si>
-    <t>0.0525,0.1346,0.7961,0.1113</t>
-  </si>
-  <si>
-    <t>0.0017,0.8984,0.8543,0.0021</t>
-  </si>
-  <si>
-    <t>0.0036,0.0189,0.9854,0.0036</t>
-  </si>
-  <si>
-    <t>0.0073,0.9617,0.1958,0.0013</t>
-  </si>
-  <si>
-    <t>0.0081,0.9836,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9165,0.0175,0.1039,0.0021</t>
-  </si>
-  <si>
-    <t>0.8564,0.0787,0.0022,0.0141</t>
-  </si>
-  <si>
-    <t>0.0045,0.0217,0.9866,0.0011</t>
-  </si>
-  <si>
-    <t>0.0024,0.3644,0.9482,0.0004</t>
-  </si>
-  <si>
-    <t>0.0114,0.3837,0.8765,0.0013</t>
-  </si>
-  <si>
-    <t>0.0025,0.9857,0.0706,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.6343,0.9343,0.0027</t>
-  </si>
-  <si>
-    <t>0.0231,0.0034,0.0075,0.9842</t>
-  </si>
-  <si>
-    <t>0.0031,0.0022,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0071,0.0041,0.0007,0.9965</t>
-  </si>
-  <si>
-    <t>0.0079,0.0021,0.0008,0.9968</t>
-  </si>
-  <si>
-    <t>0.0072,0.0021,0.0006,0.9968</t>
-  </si>
-  <si>
-    <t>0.0116,0.0012,0.0017,0.9948</t>
-  </si>
-  <si>
-    <t>0.0020,0.9239,0.7840,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.5355,0.9794,0.0004</t>
-  </si>
-  <si>
-    <t>0.0310,0.8546,0.3382,0.0057</t>
-  </si>
-  <si>
-    <t>0.0260,0.2362,0.9052,0.0057</t>
-  </si>
-  <si>
-    <t>0.0003,0.9843,0.6501,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.5433,0.8880,0.0037</t>
-  </si>
-  <si>
-    <t>0.9802,0.0103,0.0083,0.0008</t>
-  </si>
-  <si>
-    <t>0.9856,0.0118,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9838,0.0104,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9894,0.0048,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9960,0.0012,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9881,0.0066,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9856,0.0033,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9843,0.0188,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9954,0.0006,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9970,0.0004,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9961,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0005,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.0018,0.9744,0.0641</t>
-  </si>
-  <si>
-    <t>0.0618,0.0108,0.9437,0.0027</t>
-  </si>
-  <si>
-    <t>0.5798,0.0431,0.3143,0.0950</t>
-  </si>
-  <si>
-    <t>0.0535,0.0118,0.9317,0.0211</t>
-  </si>
-  <si>
-    <t>0.0109,0.9828,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.0025,0.9912,0.0188,0.0002</t>
-  </si>
-  <si>
-    <t>0.0385,0.9538,0.0037,0.0016</t>
-  </si>
-  <si>
-    <t>0.6053,0.5157,0.0151,0.0014</t>
-  </si>
-  <si>
-    <t>0.0184,0.9686,0.0069,0.0020</t>
-  </si>
-  <si>
-    <t>0.0061,0.9852,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.4141,0.6847,0.0100,0.0009</t>
-  </si>
-  <si>
-    <t>0.6258,0.1669,0.2442,0.0399</t>
-  </si>
-  <si>
-    <t>0.0241,0.0033,0.9751,0.0056</t>
-  </si>
-  <si>
-    <t>0.5904,0.2049,0.0880,0.1623</t>
-  </si>
-  <si>
-    <t>0.3406,0.2142,0.5361,0.0298</t>
-  </si>
-  <si>
-    <t>0.3442,0.0427,0.0521,0.6902</t>
-  </si>
-  <si>
-    <t>0.0024,0.9883,0.0681,0.0005</t>
-  </si>
-  <si>
-    <t>0.0064,0.9624,0.0554,0.0070</t>
-  </si>
-  <si>
-    <t>0.0082,0.9739,0.0045,0.0147</t>
-  </si>
-  <si>
-    <t>0.0030,0.8772,0.8262,0.0012</t>
-  </si>
-  <si>
-    <t>0.0514,0.9188,0.0637,0.0004</t>
-  </si>
-  <si>
-    <t>0.4458,0.4850,0.0599,0.0012</t>
-  </si>
-  <si>
-    <t>0.5861,0.5095,0.0216,0.0019</t>
-  </si>
-  <si>
-    <t>0.9909,0.0016,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9947,0.0007,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9932,0.0014,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9679,0.0225,0.0043,0.0020</t>
-  </si>
-  <si>
-    <t>0.9916,0.0017,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.8420,0.1257,0.0376,0.0008</t>
-  </si>
-  <si>
-    <t>0.9893,0.0009,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.9920,0.0013,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0023,0.7094,0.9250,0.0003</t>
-  </si>
-  <si>
-    <t>0.0100,0.2571,0.9307,0.0017</t>
-  </si>
-  <si>
-    <t>0.0289,0.0989,0.9208,0.0015</t>
-  </si>
-  <si>
-    <t>0.0319,0.2076,0.8482,0.0044</t>
-  </si>
-  <si>
-    <t>0.3775,0.1233,0.1260,0.5808</t>
-  </si>
-  <si>
-    <t>0.7185,0.0266,0.2345,0.0379</t>
-  </si>
-  <si>
-    <t>0.3122,0.0089,0.8482,0.0023</t>
-  </si>
-  <si>
-    <t>0.6835,0.0622,0.2932,0.0253</t>
-  </si>
-  <si>
-    <t>0.0310,0.0026,0.0019,0.9904</t>
-  </si>
-  <si>
-    <t>0.0005,0.0015,0.0004,0.9992</t>
-  </si>
-  <si>
-    <t>0.0039,0.0081,0.0024,0.9948</t>
-  </si>
-  <si>
-    <t>0.0291,0.0007,0.0013,0.9913</t>
-  </si>
-  <si>
-    <t>0.0034,0.8049,0.7028,0.0049</t>
-  </si>
-  <si>
-    <t>0.9225,0.0660,0.0052,0.0087</t>
-  </si>
-  <si>
-    <t>0.3767,0.6244,0.0182,0.0295</t>
-  </si>
-  <si>
-    <t>0.9821,0.0008,0.0014,0.0071</t>
-  </si>
-  <si>
-    <t>0.8265,0.1963,0.0325,0.0041</t>
-  </si>
-  <si>
-    <t>0.9670,0.0024,0.0064,0.0100</t>
-  </si>
-  <si>
-    <t>0.7882,0.0029,0.0232,0.1798</t>
-  </si>
-  <si>
-    <t>0.9694,0.0082,0.0035,0.0062</t>
-  </si>
-  <si>
-    <t>0.0054,0.0802,0.9608,0.0160</t>
-  </si>
-  <si>
-    <t>0.2989,0.0008,0.0023,0.8933</t>
-  </si>
-  <si>
-    <t>0.9285,0.0137,0.0195,0.0223</t>
-  </si>
-  <si>
-    <t>0.5347,0.4011,0.1271,0.0193</t>
-  </si>
-  <si>
-    <t>0.8831,0.0529,0.0728,0.0046</t>
-  </si>
-  <si>
-    <t>0.8939,0.0546,0.0547,0.0069</t>
-  </si>
-  <si>
-    <t>0.3374,0.5901,0.0344,0.0929</t>
-  </si>
-  <si>
-    <t>0.8417,0.2176,0.0146,0.0015</t>
-  </si>
-  <si>
-    <t>0.9203,0.0596,0.0162,0.0066</t>
-  </si>
-  <si>
-    <t>0.9843,0.0038,0.0023,0.0021</t>
-  </si>
-  <si>
-    <t>0.9580,0.0251,0.0164,0.0027</t>
-  </si>
-  <si>
-    <t>0.9935,0.0005,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9750,0.0039,0.0102,0.0047</t>
-  </si>
-  <si>
-    <t>0.9784,0.0059,0.0076,0.0023</t>
-  </si>
-  <si>
-    <t>0.9869,0.0017,0.0005,0.0025</t>
-  </si>
-  <si>
-    <t>0.9877,0.0014,0.0021,0.0028</t>
-  </si>
-  <si>
-    <t>0.9725,0.0038,0.0027,0.0090</t>
-  </si>
-  <si>
-    <t>0.8683,0.2606,0.0049,0.0010</t>
-  </si>
-  <si>
-    <t>0.8802,0.1399,0.0204,0.0019</t>
-  </si>
-  <si>
-    <t>0.5406,0.5969,0.0069,0.0010</t>
-  </si>
-  <si>
-    <t>0.3110,0.0978,0.6755,0.0056</t>
-  </si>
-  <si>
-    <t>0.9518,0.0744,0.0055,0.0006</t>
-  </si>
-  <si>
-    <t>0.9679,0.0276,0.0091,0.0011</t>
-  </si>
-  <si>
-    <t>0.9946,0.0016,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.7764,0.2504,0.0357,0.0069</t>
-  </si>
-  <si>
-    <t>0.0106,0.0181,0.9809,0.0016</t>
-  </si>
-  <si>
-    <t>0.9459,0.0156,0.0352,0.0056</t>
-  </si>
-  <si>
-    <t>0.0027,0.0019,0.9959,0.0008</t>
-  </si>
-  <si>
-    <t>0.0154,0.1293,0.9391,0.0064</t>
-  </si>
-  <si>
-    <t>0.4255,0.0201,0.7431,0.0043</t>
-  </si>
-  <si>
-    <t>0.0092,0.4514,0.9337,0.0050</t>
-  </si>
-  <si>
-    <t>0.0075,0.0088,0.9898,0.0005</t>
-  </si>
-  <si>
-    <t>0.0120,0.0062,0.9834,0.0009</t>
-  </si>
-  <si>
-    <t>0.0062,0.0048,0.9901,0.0012</t>
-  </si>
-  <si>
-    <t>0.3898,0.0287,0.7670,0.0017</t>
-  </si>
-  <si>
-    <t>0.3034,0.0149,0.8544,0.0025</t>
-  </si>
-  <si>
-    <t>0.2059,0.1081,0.7372,0.0163</t>
-  </si>
-  <si>
-    <t>0.0940,0.7483,0.1819,0.0018</t>
-  </si>
-  <si>
-    <t>0.3920,0.0808,0.6498,0.0141</t>
-  </si>
-  <si>
-    <t>0.7311,0.0174,0.3718,0.0008</t>
-  </si>
-  <si>
-    <t>0.1919,0.2131,0.6444,0.0072</t>
-  </si>
-  <si>
-    <t>0.5240,0.0394,0.5599,0.0094</t>
-  </si>
-  <si>
-    <t>0.2075,0.8179,0.0377,0.0013</t>
-  </si>
-  <si>
-    <t>0.6858,0.3370,0.0180,0.0003</t>
-  </si>
-  <si>
-    <t>0.7688,0.2862,0.0286,0.0028</t>
-  </si>
-  <si>
-    <t>0.9844,0.0101,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.8712,0.2064,0.0076,0.0010</t>
-  </si>
-  <si>
-    <t>0.5846,0.0363,0.4528,0.0170</t>
-  </si>
-  <si>
-    <t>0.8329,0.0694,0.1205,0.0021</t>
-  </si>
-  <si>
-    <t>0.6586,0.0329,0.2656,0.0560</t>
-  </si>
-  <si>
-    <t>0.4693,0.0034,0.5713,0.0175</t>
-  </si>
-  <si>
-    <t>0.5130,0.0054,0.5875,0.0112</t>
-  </si>
-  <si>
-    <t>0.0683,0.0547,0.8842,0.0133</t>
-  </si>
-  <si>
-    <t>0.0592,0.3571,0.7152,0.0440</t>
-  </si>
-  <si>
-    <t>0.0591,0.2412,0.8449,0.0074</t>
-  </si>
-  <si>
-    <t>0.1502,0.0189,0.8791,0.0059</t>
-  </si>
-  <si>
-    <t>0.0067,0.0330,0.9660,0.0109</t>
-  </si>
-  <si>
-    <t>0.9935,0.0017,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9925,0.0011,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9940,0.0013,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0009,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9877,0.0103,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9825,0.0105,0.0039,0.0009</t>
-  </si>
-  <si>
-    <t>0.9887,0.0018,0.0008,0.0021</t>
-  </si>
-  <si>
-    <t>0.9949,0.0008,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.1816,0.0080,0.8920,0.0044</t>
-  </si>
-  <si>
-    <t>0.3690,0.0342,0.7040,0.0071</t>
-  </si>
-  <si>
-    <t>0.9456,0.0140,0.0164,0.0118</t>
-  </si>
-  <si>
-    <t>0.0176,0.1056,0.9395,0.0019</t>
-  </si>
-  <si>
-    <t>0.0029,0.0214,0.9854,0.0043</t>
-  </si>
-  <si>
-    <t>0.0330,0.0220,0.9479,0.0064</t>
-  </si>
-  <si>
-    <t>0.0018,0.0010,0.9955,0.0036</t>
-  </si>
-  <si>
-    <t>0.1339,0.0124,0.8924,0.0034</t>
-  </si>
-  <si>
-    <t>0.0079,0.0135,0.9555,0.0354</t>
-  </si>
-  <si>
-    <t>0.0234,0.0120,0.9574,0.0128</t>
-  </si>
-  <si>
-    <t>0.0917,0.0137,0.9233,0.0016</t>
-  </si>
-  <si>
-    <t>0.6793,0.0134,0.4862,0.0017</t>
-  </si>
-  <si>
-    <t>0.8217,0.0017,0.1460,0.0079</t>
-  </si>
-  <si>
-    <t>0.8060,0.0010,0.0380,0.0591</t>
-  </si>
-  <si>
-    <t>0.9938,0.0029,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9653,0.0625,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9921,0.0029,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0030,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9951,0.0006,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9741,0.0153,0.0019,0.0022</t>
-  </si>
-  <si>
-    <t>0.9898,0.0048,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9947,0.0008,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0557,0.1261,0.8750,0.0144</t>
-  </si>
-  <si>
-    <t>0.0036,0.0219,0.9870,0.0014</t>
-  </si>
-  <si>
-    <t>0.0356,0.0366,0.9384,0.0106</t>
-  </si>
-  <si>
-    <t>0.0518,0.0491,0.9126,0.0008</t>
-  </si>
-  <si>
-    <t>0.0057,0.0026,0.9871,0.0063</t>
-  </si>
-  <si>
-    <t>0.2788,0.0169,0.3786,0.3465</t>
-  </si>
-  <si>
-    <t>0.3765,0.0143,0.7799,0.0029</t>
-  </si>
-  <si>
-    <t>0.0096,0.0148,0.8077,0.2889</t>
-  </si>
-  <si>
-    <t>0.9208,0.0026,0.0087,0.0525</t>
-  </si>
-  <si>
-    <t>0.0398,0.0126,0.0161,0.9719</t>
-  </si>
-  <si>
-    <t>0.0136,0.0085,0.0006,0.9942</t>
-  </si>
-  <si>
-    <t>0.0021,0.0004,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0015,0.0009,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.1051,0.1777,0.0277,0.9053</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.6176,0.0089,0.0466,0.3598</t>
+  </si>
+  <si>
+    <t>0.0139,0.0091,0.0005,0.9941</t>
+  </si>
+  <si>
+    <t>0.8424,0.0033,0.0017,0.1911</t>
+  </si>
+  <si>
+    <t>0.0352,0.0020,0.0001,0.9931</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9896,0.0022,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9950,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9889,0.0045,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9865,0.0052,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9951,0.0004,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.3934,0.3973,0.2766,0.0362</t>
+  </si>
+  <si>
+    <t>0.3592,0.0410,0.7439,0.0080</t>
+  </si>
+  <si>
+    <t>0.3700,0.0074,0.8286,0.0009</t>
+  </si>
+  <si>
+    <t>0.0400,0.0272,0.9319,0.0040</t>
+  </si>
+  <si>
+    <t>0.7283,0.0885,0.2335,0.0176</t>
+  </si>
+  <si>
+    <t>0.0073,0.9820,0.0178,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.9888,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.7708,0.3672,0.0068,0.0011</t>
+  </si>
+  <si>
+    <t>0.0128,0.9807,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.0127,0.9773,0.0072,0.0008</t>
+  </si>
+  <si>
+    <t>0.7409,0.0042,0.1432,0.0343</t>
+  </si>
+  <si>
+    <t>0.4176,0.0242,0.5735,0.0388</t>
+  </si>
+  <si>
+    <t>0.0063,0.0018,0.9906,0.0032</t>
+  </si>
+  <si>
+    <t>0.1812,0.0103,0.8886,0.0031</t>
+  </si>
+  <si>
+    <t>0.4075,0.0136,0.7445,0.0050</t>
+  </si>
+  <si>
+    <t>0.0379,0.0022,0.8367,0.1600</t>
+  </si>
+  <si>
+    <t>0.0154,0.0162,0.9485,0.0256</t>
+  </si>
+  <si>
+    <t>0.7608,0.3784,0.0092,0.0013</t>
+  </si>
+  <si>
+    <t>0.5164,0.0882,0.5237,0.0280</t>
+  </si>
+  <si>
+    <t>0.0012,0.0035,0.9838,0.0277</t>
+  </si>
+  <si>
+    <t>0.0388,0.8564,0.2477,0.0045</t>
+  </si>
+  <si>
+    <t>0.8328,0.0432,0.0744,0.0502</t>
+  </si>
+  <si>
+    <t>0.7396,0.0234,0.2207,0.0333</t>
+  </si>
+  <si>
+    <t>0.8325,0.2337,0.0178,0.0041</t>
+  </si>
+  <si>
+    <t>0.0097,0.9790,0.0530,0.0002</t>
+  </si>
+  <si>
+    <t>0.0212,0.7796,0.4257,0.0676</t>
+  </si>
+  <si>
+    <t>0.0503,0.0075,0.8707,0.0684</t>
+  </si>
+  <si>
+    <t>0.1475,0.1461,0.7234,0.0382</t>
+  </si>
+  <si>
+    <t>0.2437,0.0039,0.5007,0.1513</t>
+  </si>
+  <si>
+    <t>0.0137,0.3779,0.8947,0.0057</t>
+  </si>
+  <si>
+    <t>0.0375,0.8870,0.0911,0.0062</t>
+  </si>
+  <si>
+    <t>0.0651,0.0892,0.8733,0.0125</t>
+  </si>
+  <si>
+    <t>0.3334,0.1956,0.0318,0.5957</t>
+  </si>
+  <si>
+    <t>0.0099,0.9498,0.0474,0.0466</t>
+  </si>
+  <si>
+    <t>0.0015,0.9846,0.2172,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.9722,0.3137,0.0032</t>
+  </si>
+  <si>
+    <t>0.0191,0.0783,0.9445,0.0171</t>
+  </si>
+  <si>
+    <t>0.0002,0.2842,0.9783,0.0016</t>
+  </si>
+  <si>
+    <t>0.1964,0.0015,0.9012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0573,0.0109,0.9426,0.0044</t>
+  </si>
+  <si>
+    <t>0.0038,0.0120,0.9869,0.0031</t>
+  </si>
+  <si>
+    <t>0.0443,0.0403,0.9299,0.0090</t>
+  </si>
+  <si>
+    <t>0.9589,0.0445,0.0078,0.0013</t>
+  </si>
+  <si>
+    <t>0.9768,0.0163,0.0046,0.0012</t>
+  </si>
+  <si>
+    <t>0.9865,0.0041,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.0088,0.0253,0.9787,0.0056</t>
+  </si>
+  <si>
+    <t>0.9757,0.0053,0.0079,0.0030</t>
+  </si>
+  <si>
+    <t>0.9932,0.0031,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9820,0.0055,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.0582,0.6713,0.6805,0.0273</t>
+  </si>
+  <si>
+    <t>0.0061,0.1073,0.9618,0.0071</t>
+  </si>
+  <si>
+    <t>0.0049,0.0119,0.9587,0.0518</t>
+  </si>
+  <si>
+    <t>0.0017,0.7682,0.9624,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.0045,0.9915,0.0061</t>
+  </si>
+  <si>
+    <t>0.0478,0.8735,0.1942,0.0065</t>
+  </si>
+  <si>
+    <t>0.0144,0.9672,0.0088,0.0009</t>
+  </si>
+  <si>
+    <t>0.8788,0.0491,0.0868,0.0091</t>
+  </si>
+  <si>
+    <t>0.8630,0.1175,0.0478,0.0028</t>
+  </si>
+  <si>
+    <t>0.0175,0.0395,0.9689,0.0043</t>
+  </si>
+  <si>
+    <t>0.0053,0.6028,0.9118,0.0017</t>
+  </si>
+  <si>
+    <t>0.0027,0.7900,0.8489,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.9865,0.0759,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.7076,0.9639,0.0009</t>
+  </si>
+  <si>
+    <t>0.0241,0.0005,0.0163,0.9703</t>
+  </si>
+  <si>
+    <t>0.0047,0.0053,0.0002,0.9978</t>
+  </si>
+  <si>
+    <t>0.0018,0.0050,0.0014,0.9977</t>
+  </si>
+  <si>
+    <t>0.0318,0.0009,0.0019,0.9894</t>
+  </si>
+  <si>
+    <t>0.0085,0.0012,0.0041,0.9929</t>
+  </si>
+  <si>
+    <t>0.0059,0.0007,0.0014,0.9966</t>
+  </si>
+  <si>
+    <t>0.0004,0.9920,0.3620,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.8779,0.8001,0.0017</t>
+  </si>
+  <si>
+    <t>0.0178,0.6396,0.7833,0.0035</t>
+  </si>
+  <si>
+    <t>0.0059,0.6151,0.8665,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.9911,0.6365,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9620,0.3643,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0012,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9901,0.0042,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9836,0.0104,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9870,0.0075,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9896,0.0114,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0005,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9744,0.0256,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9928,0.0014,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0004,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9908,0.0047,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9923,0.0034,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9921,0.0007,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.0263,0.0035,0.9762,0.0038</t>
+  </si>
+  <si>
+    <t>0.0744,0.0087,0.9405,0.0043</t>
+  </si>
+  <si>
+    <t>0.8040,0.0053,0.0719,0.0442</t>
+  </si>
+  <si>
+    <t>0.1737,0.0137,0.8674,0.0111</t>
+  </si>
+  <si>
+    <t>0.0277,0.9660,0.0038,0.0006</t>
+  </si>
+  <si>
+    <t>0.0134,0.9784,0.0059,0.0006</t>
+  </si>
+  <si>
+    <t>0.0153,0.9740,0.0019,0.0046</t>
+  </si>
+  <si>
+    <t>0.4370,0.7082,0.0114,0.0014</t>
+  </si>
+  <si>
+    <t>0.0240,0.9587,0.0111,0.0041</t>
+  </si>
+  <si>
+    <t>0.0075,0.9845,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.7117,0.4842,0.0017,0.0009</t>
+  </si>
+  <si>
+    <t>0.4965,0.1474,0.5001,0.0340</t>
+  </si>
+  <si>
+    <t>0.2607,0.0273,0.7751,0.0170</t>
+  </si>
+  <si>
+    <t>0.6492,0.0304,0.3645,0.0187</t>
+  </si>
+  <si>
+    <t>0.4241,0.1714,0.4899,0.0096</t>
+  </si>
+  <si>
+    <t>0.1043,0.1696,0.0115,0.8429</t>
+  </si>
+  <si>
+    <t>0.0116,0.9630,0.0645,0.0046</t>
+  </si>
+  <si>
+    <t>0.0088,0.9718,0.0653,0.0015</t>
+  </si>
+  <si>
+    <t>0.0052,0.9803,0.0072,0.0040</t>
+  </si>
+  <si>
+    <t>0.0151,0.9201,0.2515,0.0042</t>
+  </si>
+  <si>
+    <t>0.0340,0.9368,0.0808,0.0004</t>
+  </si>
+  <si>
+    <t>0.9201,0.1001,0.0154,0.0012</t>
+  </si>
+  <si>
+    <t>0.5144,0.4788,0.0496,0.0023</t>
+  </si>
+  <si>
+    <t>0.9905,0.0018,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.9821,0.0049,0.0045,0.0020</t>
+  </si>
+  <si>
+    <t>0.9951,0.0005,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9843,0.0024,0.0015,0.0032</t>
+  </si>
+  <si>
+    <t>0.9934,0.0014,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0103,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9730,0.0023,0.0020,0.0093</t>
+  </si>
+  <si>
+    <t>0.9698,0.0145,0.0154,0.0013</t>
+  </si>
+  <si>
+    <t>0.0119,0.2333,0.9538,0.0004</t>
+  </si>
+  <si>
+    <t>0.0152,0.7065,0.6185,0.0011</t>
+  </si>
+  <si>
+    <t>0.0157,0.0548,0.9647,0.0003</t>
+  </si>
+  <si>
+    <t>0.1468,0.0938,0.7766,0.0066</t>
+  </si>
+  <si>
+    <t>0.7202,0.0443,0.1506,0.0776</t>
+  </si>
+  <si>
+    <t>0.2100,0.0666,0.1461,0.7316</t>
+  </si>
+  <si>
+    <t>0.3960,0.0054,0.8064,0.0018</t>
+  </si>
+  <si>
+    <t>0.5573,0.3330,0.1454,0.0632</t>
+  </si>
+  <si>
+    <t>0.0250,0.0015,0.0018,0.9919</t>
+  </si>
+  <si>
+    <t>0.0006,0.0020,0.0002,0.9994</t>
+  </si>
+  <si>
+    <t>0.0028,0.0034,0.0018,0.9965</t>
+  </si>
+  <si>
+    <t>0.0086,0.0062,0.0003,0.9965</t>
+  </si>
+  <si>
+    <t>0.0015,0.6125,0.8976,0.0053</t>
+  </si>
+  <si>
+    <t>0.9702,0.0214,0.0010,0.0034</t>
+  </si>
+  <si>
+    <t>0.6495,0.3921,0.0359,0.0080</t>
+  </si>
+  <si>
+    <t>0.9763,0.0067,0.0011,0.0041</t>
+  </si>
+  <si>
+    <t>0.9307,0.0656,0.0173,0.0025</t>
+  </si>
+  <si>
+    <t>0.9620,0.0202,0.0052,0.0045</t>
+  </si>
+  <si>
+    <t>0.8675,0.0075,0.0222,0.0764</t>
+  </si>
+  <si>
+    <t>0.9711,0.0027,0.0006,0.0138</t>
+  </si>
+  <si>
+    <t>0.0030,0.0600,0.9732,0.0110</t>
+  </si>
+  <si>
+    <t>0.6784,0.0025,0.0033,0.4945</t>
+  </si>
+  <si>
+    <t>0.8904,0.0070,0.0059,0.0973</t>
+  </si>
+  <si>
+    <t>0.8131,0.1492,0.0575,0.0087</t>
+  </si>
+  <si>
+    <t>0.8988,0.0661,0.0223,0.0059</t>
+  </si>
+  <si>
+    <t>0.8496,0.1562,0.0378,0.0045</t>
+  </si>
+  <si>
+    <t>0.3075,0.4822,0.3058,0.0159</t>
+  </si>
+  <si>
+    <t>0.1714,0.7015,0.1025,0.0029</t>
+  </si>
+  <si>
+    <t>0.8448,0.1500,0.0317,0.0036</t>
+  </si>
+  <si>
+    <t>0.9906,0.0016,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9557,0.0061,0.0016,0.0208</t>
+  </si>
+  <si>
+    <t>0.9949,0.0004,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9895,0.0004,0.0004,0.0047</t>
+  </si>
+  <si>
+    <t>0.9877,0.0060,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9693,0.0332,0.0059,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0003,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9799,0.0025,0.0008,0.0078</t>
+  </si>
+  <si>
+    <t>0.7676,0.3997,0.0025,0.0010</t>
+  </si>
+  <si>
+    <t>0.8566,0.1994,0.0124,0.0008</t>
+  </si>
+  <si>
+    <t>0.5637,0.6056,0.0048,0.0017</t>
+  </si>
+  <si>
+    <t>0.4569,0.5157,0.1078,0.0074</t>
+  </si>
+  <si>
+    <t>0.9861,0.0081,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9084,0.0787,0.0336,0.0050</t>
+  </si>
+  <si>
+    <t>0.9811,0.0107,0.0044,0.0008</t>
+  </si>
+  <si>
+    <t>0.6914,0.3258,0.0054,0.0132</t>
+  </si>
+  <si>
+    <t>0.0052,0.0181,0.9908,0.0007</t>
+  </si>
+  <si>
+    <t>0.9402,0.0682,0.0134,0.0018</t>
+  </si>
+  <si>
+    <t>0.0019,0.0026,0.9950,0.0012</t>
+  </si>
+  <si>
+    <t>0.0153,0.0809,0.9625,0.0034</t>
+  </si>
+  <si>
+    <t>0.0992,0.0041,0.9472,0.0007</t>
+  </si>
+  <si>
+    <t>0.0357,0.0813,0.9368,0.0116</t>
+  </si>
+  <si>
+    <t>0.0153,0.0088,0.9831,0.0009</t>
+  </si>
+  <si>
+    <t>0.0102,0.0030,0.9881,0.0010</t>
+  </si>
+  <si>
+    <t>0.0045,0.0048,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0491,0.0122,0.9482,0.0033</t>
+  </si>
+  <si>
+    <t>0.1079,0.0196,0.9264,0.0019</t>
+  </si>
+  <si>
+    <t>0.1545,0.0461,0.8244,0.0076</t>
+  </si>
+  <si>
+    <t>0.5169,0.1739,0.4388,0.0247</t>
+  </si>
+  <si>
+    <t>0.4003,0.0890,0.6013,0.0055</t>
+  </si>
+  <si>
+    <t>0.5588,0.1177,0.4110,0.0061</t>
+  </si>
+  <si>
+    <t>0.6847,0.0530,0.3785,0.0060</t>
+  </si>
+  <si>
+    <t>0.5819,0.0370,0.5565,0.0028</t>
+  </si>
+  <si>
+    <t>0.4755,0.6529,0.0122,0.0035</t>
+  </si>
+  <si>
+    <t>0.3453,0.7873,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.4035,0.7339,0.0034,0.0018</t>
+  </si>
+  <si>
+    <t>0.9530,0.0622,0.0048,0.0018</t>
+  </si>
+  <si>
+    <t>0.9462,0.0653,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.6224,0.0862,0.4412,0.0151</t>
+  </si>
+  <si>
+    <t>0.8095,0.0136,0.2556,0.0029</t>
+  </si>
+  <si>
+    <t>0.7219,0.0208,0.0315,0.2110</t>
+  </si>
+  <si>
+    <t>0.7501,0.0243,0.2320,0.0202</t>
+  </si>
+  <si>
+    <t>0.8059,0.0074,0.2724,0.0034</t>
+  </si>
+  <si>
+    <t>0.0989,0.0234,0.9009,0.0078</t>
+  </si>
+  <si>
+    <t>0.0253,0.2941,0.8766,0.0168</t>
+  </si>
+  <si>
+    <t>0.0382,0.0880,0.9209,0.0173</t>
+  </si>
+  <si>
+    <t>0.1826,0.0435,0.3527,0.4565</t>
+  </si>
+  <si>
+    <t>0.0282,0.1262,0.8917,0.0288</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9893,0.0056,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0008,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9726,0.0317,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9932,0.0019,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9888,0.0094,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0000,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9842,0.0053,0.0041,0.0014</t>
+  </si>
+  <si>
+    <t>0.0080,0.0029,0.9926,0.0007</t>
+  </si>
+  <si>
+    <t>0.4104,0.1234,0.5597,0.0370</t>
+  </si>
+  <si>
+    <t>0.9074,0.0145,0.0344,0.0225</t>
+  </si>
+  <si>
+    <t>0.0365,0.0351,0.9573,0.0022</t>
+  </si>
+  <si>
+    <t>0.0017,0.0101,0.9944,0.0012</t>
+  </si>
+  <si>
+    <t>0.0605,0.0021,0.9690,0.0009</t>
+  </si>
+  <si>
+    <t>0.0091,0.0023,0.9864,0.0047</t>
+  </si>
+  <si>
+    <t>0.1020,0.0105,0.9217,0.0016</t>
+  </si>
+  <si>
+    <t>0.0055,0.0095,0.9715,0.0226</t>
+  </si>
+  <si>
+    <t>0.0440,0.0263,0.9364,0.0011</t>
+  </si>
+  <si>
+    <t>0.2075,0.0117,0.8782,0.0023</t>
+  </si>
+  <si>
+    <t>0.6018,0.0243,0.3036,0.0740</t>
+  </si>
+  <si>
+    <t>0.5191,0.0011,0.2846,0.0384</t>
+  </si>
+  <si>
+    <t>0.7826,0.0148,0.1183,0.0441</t>
+  </si>
+  <si>
+    <t>0.9948,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9939,0.0047,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9894,0.0049,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9937,0.0033,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9928,0.0002,0.0001,0.0035</t>
+  </si>
+  <si>
+    <t>0.9950,0.0020,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9796,0.0256,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9936,0.0025,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0078,0.0434,0.9714,0.0004</t>
+  </si>
+  <si>
+    <t>0.0049,0.0156,0.9861,0.0021</t>
+  </si>
+  <si>
+    <t>0.0078,0.0116,0.9757,0.0140</t>
+  </si>
+  <si>
+    <t>0.1440,0.0434,0.8569,0.0044</t>
+  </si>
+  <si>
+    <t>0.0034,0.0083,0.9863,0.0058</t>
+  </si>
+  <si>
+    <t>0.1353,0.0227,0.7088,0.2494</t>
+  </si>
+  <si>
+    <t>0.1048,0.0125,0.9093,0.0042</t>
+  </si>
+  <si>
+    <t>0.0230,0.0216,0.8028,0.2194</t>
+  </si>
+  <si>
+    <t>0.6243,0.0070,0.0044,0.5783</t>
+  </si>
+  <si>
+    <t>0.0314,0.0120,0.0101,0.9787</t>
+  </si>
+  <si>
+    <t>0.0086,0.0068,0.0045,0.9917</t>
+  </si>
+  <si>
+    <t>0.0070,0.0002,0.0005,0.9975</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.4906,0.1206,0.0271,0.4340</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2118,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2216,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2510,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2584,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2944,10 +2959,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3126,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3154,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3532,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3546,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3588,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3658,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3700,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3882,10 +3897,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4022,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4120,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4190,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4204,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4372,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4708,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4722,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4876,10 +4891,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5436,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5506,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
